--- a/stories/arbres/TREE-SAN-004.xlsx
+++ b/stories/arbres/TREE-SAN-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès joue dans le jardin. Papa est là. Maman arrive avec un panier. Les mains d'Inès ont de la terre. Bientôt on goûte. Avant de manger, on lave les mains. Savon et eau. Après les toilettes, c'est pareil. Savon, puis rincer, puis essuyer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a construit une tour de cubes, dans l'herbe. Les cubes ont un peu de terre. Papa dit : on va manger. Avant de manger, Inès va au robinet du jardin. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Après les toilettes, tout à l'heure, elle avait déjà lavé avec du savon.</t>
+          <t>Inès a construit une tour de cubes, dans l'herbe. Les cubes ont un peu de terre. On va manger. Avant de manger, Inès va au robinet du jardin. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Après les toilettes, tout à l'heure, elle avait déjà lavé avec du savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a construit une tour de cubes, dans l'herbe. Les cubes ont un peu de terre.
+papa|On va manger. Avant de manger, Inès va au robinet du jardin. Elle ouvre l'eau.
+narrateur|Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Après les toilettes, tout à l'heure, elle avait déjà lavé avec du savon.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains d'Inès sentent le savon. Avant de manger, c'est fait. Après les toilettes, c'était fait aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2227,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maman sort une pomme. Inès a les mains propres. Avant de manger, elle a pris le savon. Après les toilettes, elle avait fait pareil. Elle croque. La pomme est croquante.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat frotte sa tête. Inès a les mains propres. Avant de manger, savon. Après les toilettes, savon. Elle mange sa pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien s'assoit dans l'herbe. Inès a pris le savon avant de manger. Après les toilettes aussi. La pomme craque.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|La poule picore loin. Inès a les mains savonnées. Avant de manger. Après les toilettes. Elle finit sa pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ouvre un yaourt. Inès a lavé. Savon, avant de manger. Savon, après les toilettes. Elle prend sa cuillère. Le yaourt est frais.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4112,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat miaule. Inès a les mains propres grâce au savon. Avant de manger. Après les toilettes. Elle mange son yaourt.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien respire fort. Inès a pris le savon. Avant de manger, après les toilettes. Le yaourt est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule fait cot cot. Inès a lavé au savon. Avant de manger. Après les toilettes. Elle range la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maman casse le pain. Inès a les mains propres. Avant de manger, savon. Après les toilettes, savon. Elle mange un morceau. Ça sent le four.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat s'enroule. Inès a pris le savon avant de manger. Après les toilettes aussi. Le pain est bon.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien pose la tête. Inès a les mains savonnées. Avant de manger. Après les toilettes. Elle dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6140,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|La poule s'éloigne. Inès a lavé. Savon avant de manger. Savon après les toilettes. Elle range le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6307,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6336,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inès a lu un livre sur la couverture, au jardin. Elle va aux toilettes de la maison. Après les toilettes, elle prend le savon. Eau, savon, rincer, essuyer. Puis maman dit : avant de manger, on lave encore. Inès reprend le savon.</t>
+          <t>Inès a lu un livre sur la couverture, au jardin. Elle va aux toilettes de la maison. Après les toilettes, elle prend le savon. Eau, savon, rincer, essuyer. Puis Avant de manger, on lave encore. Inès reprend le savon.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6474,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a lu un livre sur la couverture, au jardin. Elle va aux toilettes de la maison. Après les toilettes, elle prend le savon. Eau, savon, rincer, essuyer. Puis
+maman|Avant de manger, on lave encore.
+narrateur|Inès reprend le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Inès prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre attend. Les mains d'Inès sentent le savon. Après les toilettes, c'est fait. Avant de manger, c'est fait.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a fermé le livre. Elle a pris le savon après les toilettes. Avant de manger la pomme, elle lave encore. Savon. Puis elle croque.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7383,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7550,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat se couche sur le livre. Inès a le savon sur les mains. Après les toilettes. Avant de manger. La pomme est rouge.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7717,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7884,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien écoute l'histoire. Inès a lavé au savon. Après les toilettes, avant de manger. Elle mange sa pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8051,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8218,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|La poule s'approche du panier. Inès a pris le savon. Après les toilettes. Avant de manger.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8385,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8552,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose le yaourt près du livre. Inès a le savon après les toilettes. Avant de manger, elle frotte encore. Puis elle mange.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8743,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8910,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat lèche sa patte. Inès a pris le savon. Après les toilettes. Avant de manger. Le yaourt est frais.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9077,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9244,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien bâille. Inès a les mains savonnées. Après les toilettes, avant de manger. Elle range le pot.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9411,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9578,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule picore une miette loin. Inès a lavé au savon. Après les toilettes. Avant de manger.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9745,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9912,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose le pain sur la couverture. Inès a lavé après les toilettes, avec du savon. Avant de manger, elle lave encore. Puis elle croque.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10103,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10270,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat s'étire. Inès a le savon. Après les toilettes. Avant de manger. Le pain sent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10437,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10604,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien garde le livre. Inès a pris le savon. Après les toilettes, avant de manger. Elle dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10771,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10938,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|La poule fait un petit bruit. Inès a lavé. Savon après les toilettes. Savon avant de manger.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11105,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11134,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Inès a fait la dînette dans le jardin. Petites assiettes. Maman dit : maintenant, le vrai goûter. Avant de manger, Inès ouvre l'eau. Elle prend le savon. Elle se souvient : après les toilettes, le savon aussi. Elle rince. Elle essuie.</t>
+          <t>Inès a fait la dînette dans le jardin. Petites assiettes. Maintenant, le vrai goûter. Avant de manger, Inès ouvre l'eau. Elle prend le savon. Elle se souvient : après les toilettes, le savon aussi. Elle rince. Elle essuie.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11272,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a fait la dînette dans le jardin. Petites assiettes.
+maman|Maintenant, le vrai goûter. Avant de manger, Inès ouvre l'eau.
+narrateur|Elle prend le savon. Elle se souvient : après les toilettes, le savon aussi. Elle rince. Elle essuie.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11459,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Avant le vrai goûter, Inès prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11632,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette est rangée. Les vraies mains sont propres. Savon avant de manger. Savon après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11823,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11990,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose les petites assiettes. Puis elle lave. Savon, avant de manger la pomme. Après les toilettes, elle savait déjà : savon. Elle croque.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12181,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12348,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat joue avec une cuillère en bois. Inès a pris le savon. Avant de manger. Après les toilettes. La pomme craque.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12515,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12682,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien reste près de papa. Inès a le savon. Avant de manger, après les toilettes. Elle mange sa pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12849,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13016,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|La poule regarde la dînette. Inès a lavé au savon. Avant de manger. Après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13183,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13350,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le yaourt n'est pas en plastique. C'est le vrai. Inès a le savon avant de manger. Après les toilettes, savon aussi. Elle prend sa cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13541,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13708,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat s'assoit droit. Inès a les mains savonnées. Avant de manger. Après les toilettes. Le yaourt est bon.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13875,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14042,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien cligne. Inès a pris le savon. Avant de manger, après les toilettes. Elle range.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14209,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14376,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule s'éloigne. Inès a lavé. Savon avant de manger. Savon après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14543,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14710,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne le vrai pain. Inès a lavé. Savon avant de manger. Savon après les toilettes. Elle mange. La dînette attend dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14901,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15068,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat ferme les yeux. Inès a pris le savon. Avant de manger. Après les toilettes. Le pain est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15235,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15402,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien suit maman. Inès a le savon. Avant de manger, après les toilettes. Elle dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15569,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15736,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|La poule retourne au fond. Inès a lavé au savon. Avant de manger. Après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15903,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15943,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-004.xlsx
+++ b/stories/arbres/TREE-SAN-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Inès joue dans le jardin. Papa est là. Maman arrive avec un panier. Les mains d'Inès ont de la terre. Bientôt on goûte. Avant de manger, on lave les mains. Savon et eau. Après les toilettes, c'est pareil. Savon, puis rincer, puis essuyer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 narrateur|Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Après les toilettes, tout à l'heure, elle avait déjà lavé avec du savon.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Inès se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Les mains d'Inès sentent le savon. Avant de manger, c'est fait. Après les toilettes, c'était fait aussi.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Maman sort une pomme. Inès a les mains propres. Avant de manger, elle a pris le savon. Après les toilettes, elle avait fait pareil. Elle croque. La pomme est croquante.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2757,6 +2774,7 @@
           <t>narrateur|Le chat frotte sa tête. Inès a les mains propres. Avant de manger, savon. Après les toilettes, savon. Elle mange sa pomme.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3110,11 @@
           <t>narrateur|Le chien s'assoit dans l'herbe. Inès a pris le savon avant de manger. Après les toilettes aussi. La pomme craque.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3450,7 @@
           <t>narrateur|La poule picore loin. Inès a les mains savonnées. Avant de manger. Après les toilettes. Elle finit sa pomme.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3786,7 @@
           <t>narrateur|Papa ouvre un yaourt. Inès a lavé. Savon, avant de manger. Savon, après les toilettes. Elle prend sa cuillère. Le yaourt est frais.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3948,6 +3976,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4117,6 +4150,7 @@
           <t>narrateur|Le chat miaule. Inès a les mains propres grâce au savon. Avant de manger. Après les toilettes. Elle mange son yaourt.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4486,11 @@
           <t>narrateur|Le chien respire fort. Inès a pris le savon. Avant de manger, après les toilettes. Le yaourt est doux.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4826,7 @@
           <t>narrateur|La poule fait cot cot. Inès a lavé au savon. Avant de manger. Après les toilettes. Elle range la cuillère.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5162,7 @@
           <t>narrateur|Maman casse le pain. Inès a les mains propres. Avant de manger, savon. Après les toilettes, savon. Elle mange un morceau. Ça sent le four.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5308,6 +5352,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5477,6 +5526,7 @@
           <t>narrateur|Le chat s'enroule. Inès a pris le savon avant de manger. Après les toilettes aussi. Le pain est bon.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5862,11 @@
           <t>narrateur|Le chien pose la tête. Inès a les mains savonnées. Avant de manger. Après les toilettes. Elle dit merci.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6202,7 @@
           <t>narrateur|La poule s'éloigne. Inès a lavé. Savon avant de manger. Savon après les toilettes. Elle range le pain.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6370,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6540,7 @@
 narrateur|Inès reprend le savon.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6728,7 @@
           <t>narrateur|Après les toilettes, Inès prend quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6900,7 @@
           <t>narrateur|Le livre attend. Les mains d'Inès sentent le savon. Après les toilettes, c'est fait. Avant de manger, c'est fait.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7092,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7260,7 @@
           <t>narrateur|Inès a fermé le livre. Elle a pris le savon après les toilettes. Avant de manger la pomme, elle lave encore. Savon. Puis elle croque.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7450,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7555,6 +7624,7 @@
           <t>narrateur|Le chat se couche sur le livre. Inès a le savon sur les mains. Après les toilettes. Avant de manger. La pomme est rouge.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7722,6 +7792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7889,6 +7960,11 @@
           <t>narrateur|Le chien écoute l'histoire. Inès a lavé au savon. Après les toilettes, avant de manger. Elle mange sa pomme.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8056,6 +8132,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8223,6 +8300,7 @@
           <t>narrateur|La poule s'approche du panier. Inès a pris le savon. Après les toilettes. Avant de manger.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8390,6 +8468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8557,6 +8636,7 @@
           <t>narrateur|Papa pose le yaourt près du livre. Inès a le savon après les toilettes. Avant de manger, elle frotte encore. Puis elle mange.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8826,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8915,6 +9000,7 @@
           <t>narrateur|Le chat lèche sa patte. Inès a pris le savon. Après les toilettes. Avant de manger. Le yaourt est frais.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9082,6 +9168,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9249,6 +9336,11 @@
           <t>narrateur|Le chien bâille. Inès a les mains savonnées. Après les toilettes, avant de manger. Elle range le pot.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9416,6 +9508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9583,6 +9676,7 @@
           <t>narrateur|La poule picore une miette loin. Inès a lavé au savon. Après les toilettes. Avant de manger.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9750,6 +9844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9917,6 +10012,7 @@
           <t>narrateur|Maman pose le pain sur la couverture. Inès a lavé après les toilettes, avec du savon. Avant de manger, elle lave encore. Puis elle croque.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10202,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10275,6 +10376,7 @@
           <t>narrateur|Le chat s'étire. Inès a le savon. Après les toilettes. Avant de manger. Le pain sent bon.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10544,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10609,6 +10712,11 @@
           <t>narrateur|Le chien garde le livre. Inès a pris le savon. Après les toilettes, avant de manger. Elle dit merci.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10776,6 +10884,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10943,6 +11052,7 @@
           <t>narrateur|La poule fait un petit bruit. Inès a lavé. Savon après les toilettes. Savon avant de manger.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11110,6 +11220,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11279,6 +11390,7 @@
 narrateur|Elle prend le savon. Elle se souvient : après les toilettes, le savon aussi. Elle rince. Elle essuie.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11466,6 +11578,7 @@
           <t>narrateur|Avant le vrai goûter, Inès prend quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11637,6 +11750,7 @@
           <t>narrateur|La dînette est rangée. Les vraies mains sont propres. Savon avant de manger. Savon après les toilettes.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11828,6 +11942,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11995,6 +12110,7 @@
           <t>narrateur|Inès pose les petites assiettes. Puis elle lave. Savon, avant de manger la pomme. Après les toilettes, elle savait déjà : savon. Elle croque.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12184,6 +12300,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12353,6 +12474,7 @@
           <t>narrateur|Le chat joue avec une cuillère en bois. Inès a pris le savon. Avant de manger. Après les toilettes. La pomme craque.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12520,6 +12642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12687,6 +12810,11 @@
           <t>narrateur|Le chien reste près de papa. Inès a le savon. Avant de manger, après les toilettes. Elle mange sa pomme.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12854,6 +12982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13021,6 +13150,7 @@
           <t>narrateur|La poule regarde la dînette. Inès a lavé au savon. Avant de manger. Après les toilettes.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13188,6 +13318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13486,7 @@
           <t>narrateur|Le yaourt n'est pas en plastique. C'est le vrai. Inès a le savon avant de manger. Après les toilettes, savon aussi. Elle prend sa cuillère.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13544,6 +13676,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13713,6 +13850,7 @@
           <t>narrateur|Le chat s'assoit droit. Inès a les mains savonnées. Avant de manger. Après les toilettes. Le yaourt est bon.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13880,6 +14018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14047,6 +14186,11 @@
           <t>narrateur|Le chien cligne. Inès a pris le savon. Avant de manger, après les toilettes. Elle range.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14214,6 +14358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14381,6 +14526,7 @@
           <t>narrateur|La poule s'éloigne. Inès a lavé. Savon avant de manger. Savon après les toilettes.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14548,6 +14694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14715,6 +14862,7 @@
           <t>narrateur|Maman donne le vrai pain. Inès a lavé. Savon avant de manger. Savon après les toilettes. Elle mange. La dînette attend dans la caisse.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14904,6 +15052,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15073,6 +15226,7 @@
           <t>narrateur|Le chat ferme les yeux. Inès a pris le savon. Avant de manger. Après les toilettes. Le pain est doux.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15240,6 +15394,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15407,6 +15562,11 @@
           <t>narrateur|Le chien suit maman. Inès a le savon. Avant de manger, après les toilettes. Elle dit merci.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15574,6 +15734,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15741,6 +15902,7 @@
           <t>narrateur|La poule retourne au fond. Inès a lavé au savon. Avant de manger. Après les toilettes.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15908,6 +16070,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15926,7 +16089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15950,6 +16113,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16151,6 +16328,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
